--- a/DNEL/results/results_multicut.xlsx
+++ b/DNEL/results/results_multicut.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jagan024\Desktop\CCG-RODDU\DNEL\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C7AEDC-730C-4672-8D73-8926B50F72A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A6C08D-DC4F-43EE-B51F-BD33D16D66B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="3285" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,21 @@
     <sheet name="39bus" sheetId="3" r:id="rId3"/>
     <sheet name="118bus" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -505,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
@@ -516,7 +527,7 @@
     <col min="7" max="7" width="14.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -539,7 +550,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>5</v>
       </c>
@@ -565,7 +576,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" t="s">
         <v>2</v>
@@ -588,8 +599,12 @@
       <c r="H3" t="s">
         <v>23</v>
       </c>
+      <c r="J3">
+        <f>(C3-C4)/C3</f>
+        <v>0.13224246083516614</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
       <c r="B4" t="s">
         <v>3</v>
@@ -613,7 +628,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>39</v>
       </c>
@@ -639,7 +654,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" t="s">
         <v>2</v>
@@ -662,8 +677,12 @@
       <c r="H6" t="s">
         <v>23</v>
       </c>
+      <c r="J6">
+        <f>(C6-C7)/C6</f>
+        <v>0.94682950669286314</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" t="s">
         <v>3</v>
@@ -687,7 +706,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>188</v>
       </c>
@@ -713,7 +732,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" t="s">
         <v>2</v>
@@ -736,8 +755,12 @@
       <c r="H9" t="s">
         <v>23</v>
       </c>
+      <c r="J9">
+        <f>(C9-C10)/C9</f>
+        <v>0.83414851922498667</v>
+      </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" t="s">
         <v>3</v>
